--- a/artfynd/A 42860-2022 artfynd.xlsx
+++ b/artfynd/A 42860-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42860-2022 artfynd.xlsx
+++ b/artfynd/A 42860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6456183</v>
+        <v>58556669</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225046</v>
+        <v>1444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Sarcoscypha coccinea s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lisjö kyrka, Surahammars kn, Vstm</t>
+          <t>Lisjö Bruk, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559345.220985755</v>
+        <v>559372</v>
       </c>
       <c r="R2" t="n">
-        <v>6618599.886469234</v>
+        <v>6618635</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-10-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,82 +764,77 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövskogsdunge</t>
+          <t>Frodig bäckkant</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Lövved</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström, Jesper Gustavsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3478938</v>
+        <v>120408441</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>4379</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lisjö kyrka, Surahammars kn, Vstm</t>
+          <t>Lisjö Bruk, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559345.220985755</v>
+        <v>559467</v>
       </c>
       <c r="R3" t="n">
-        <v>6618599.886469234</v>
+        <v>6618643</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-10-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,38 +875,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lövskogsdunge</t>
+          <t>Välklippt gräsmatta</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58556669</v>
+        <v>120408437</v>
       </c>
       <c r="B4" t="n">
-        <v>81961</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,47 +910,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1444</v>
+        <v>4398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lisjö Bruk, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559372.471467315</v>
+        <v>559467</v>
       </c>
       <c r="R4" t="n">
-        <v>6618635.150098072</v>
+        <v>6618643</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,12 +983,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Frodig bäckkant</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Lövved</t>
+          <t>Välklippt gräsmatta</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,10 +994,531 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström, Jesper Gustavsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3477320</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lisjö kyrka, Sura sn, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559465</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618640</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-08-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-08-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandlövskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3478938</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lisjö kyrka, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559345</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618600</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2009-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2009-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövskogsdunge</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3478939</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lisjö kyrka, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559384</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6618674</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2009-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2009-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövskogsdunge</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6456183</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lisjö kyrka, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559345</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618600</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2009-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2009-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lövskogsdunge</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6456184</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lisjö kyrka, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>559384</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6618674</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2009-10-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2009-10-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövskogsdunge</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42860-2022 artfynd.xlsx
+++ b/artfynd/A 42860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58556669</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120408441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120408437</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3477320</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3478938</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3478939</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6456183</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,8 +1559,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6456184</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>